--- a/product_selector_out/STM32WB0 series.xlsx
+++ b/product_selector_out/STM32WB0 series.xlsx
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb05kz.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb09ke.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Arm Cortex-M0+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb05kn.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6405,9 +6405,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6747,9 +6747,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7009,9 +7009,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AZ17" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AZ17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA17" s="6" t="inlineStr">
@@ -7089,9 +7089,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7431,9 +7431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8115,9 +8115,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8142,9 +8142,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -8457,9 +8457,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8531,28 +8531,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32WB05TZ</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32WB0 series.xlsx
+++ b/product_selector_out/STM32WB0 series.xlsx
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb05kz.pdf</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb09ke.pdf</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Arm Cortex-M0+</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb05kn.pdf</t>
         </is>
       </c>
     </row>
@@ -6405,9 +6405,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6747,9 +6747,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7009,9 +7009,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AZ17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AZ17" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="BA17" s="6" t="inlineStr">
@@ -7089,9 +7089,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7431,9 +7431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8115,9 +8115,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8142,9 +8142,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -8457,9 +8457,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8531,6 +8531,28 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32WB05TZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32WB0 series.xlsx
+++ b/product_selector_out/STM32WB0 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BQ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.15234375" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1011,6 +1017,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1350,6 +1357,11 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
@@ -1692,6 +1704,11 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb09ke.pdf</t>
         </is>
       </c>
@@ -2034,6 +2051,11 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb05kz.pdf</t>
         </is>
       </c>
@@ -2379,6 +2401,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2721,6 +2748,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3063,6 +3095,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3405,6 +3442,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3744,6 +3786,11 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb05kn.pdf</t>
         </is>
       </c>
@@ -4089,6 +4136,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4431,9 +4483,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4456,14 +4513,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4481,6 +4537,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -4493,6 +4550,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -4525,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BQ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4596,6 +4654,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4944,6 +5003,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5042,6 +5106,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5379,7 +5444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5721,7 +5791,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
+      <c r="BP13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6063,7 +6138,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
+      <c r="BP14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6410,6 +6490,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -6752,6 +6837,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7094,6 +7184,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7436,6 +7531,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7773,7 +7873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
+      <c r="BP19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8120,6 +8225,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8462,11 +8572,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
